--- a/ci-build/ValueSet-enlist-change-type.xlsx
+++ b/ci-build/ValueSet-enlist-change-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:16:40+00:00</t>
+    <t>2026-07-31T13:26:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-enlist-change-type.xlsx
+++ b/ci-build/ValueSet-enlist-change-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:26:52+00:00</t>
+    <t>2026-07-31T13:33:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-enlist-change-type.xlsx
+++ b/ci-build/ValueSet-enlist-change-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:33:02+00:00</t>
+    <t>2026-07-31T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-enlist-change-type.xlsx
+++ b/ci-build/ValueSet-enlist-change-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:38:59+00:00</t>
+    <t>2026-07-31T13:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-enlist-change-type.xlsx
+++ b/ci-build/ValueSet-enlist-change-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:45:11+00:00</t>
+    <t>2026-07-31T14:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-enlist-change-type.xlsx
+++ b/ci-build/ValueSet-enlist-change-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:14:54+00:00</t>
+    <t>2026-07-31T14:25:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-enlist-change-type.xlsx
+++ b/ci-build/ValueSet-enlist-change-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:25:45+00:00</t>
+    <t>2026-08-02T18:42:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-enlist-change-type.xlsx
+++ b/ci-build/ValueSet-enlist-change-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:42:01+00:00</t>
+    <t>2026-08-02T18:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-enlist-change-type.xlsx
+++ b/ci-build/ValueSet-enlist-change-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:51:55+00:00</t>
+    <t>2026-08-03T05:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
